--- a/rwa-with-ui/Backend/docs/decision-trees/Issue Types and Steps.xlsx
+++ b/rwa-with-ui/Backend/docs/decision-trees/Issue Types and Steps.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3eca242bee5b4d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7236abcc79924b5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -310,7 +310,7 @@
       </x:c>
       <x:c r="B2" s="15" t="str">
         <x:v>{
-    "1": "Scope the case to the GFC ID in the email. Query om_cdm_rwa_mtrc where OBLG_ID equals that GFC ID. If no rows exist, STOP: the Mart has no data for the requested counterparty and the issue must be traced to the upstream/source load; otherwise continue.",
+    "1": "Scope the case to the GFC ID in the email. Query om_cdm_rwa_mtrc where OBLG_ID equals that GFC ID. If the email also supplies SCR_ID and/or src_txn_id, restrict the investigation to those matching rows so other securities/transactions under the same GFC ID do not contaminate the case. If no rows exist for the requested scope, STOP: the Mart has no data for the requested counterparty/security/transaction and the issue must be traced to the upstream/source load; otherwise continue.",
     "2": "From those Mart rows, keep BAL_TYP_CD 15 or 16, which are the inbound collateral balance types used by this demo. If neither balance type exists, STOP: no inbound collateral balance was received for this GFC ID; otherwise continue.",
     "3": "Check FDL_FX_AMT on the selected rows. If every amount is blank or zero, STOP: the upstream collateral balance is missing/zero. If amounts exist, record the total and the amount by SCR_ID and src_txn_id, then continue.",
     "4": "Check BUY_SELL_IND across the selected rows. If the values are mixed or inconsistent with the inbound population expected by the application, STOP and report a direction/sign mapping issue with the affected src_txn_id values; otherwise continue.",
@@ -326,15 +326,15 @@
     "14": "Check stale_prc_flg_2days in Mart Extn. If any relevant value='Y', STOP: the collateral price is stale beyond the short-term threshold and recognition is reduced/blocked. Report the affected balance type and Mart collateral amount. Otherwise continue.",
     "15": "Check stale_prc_flg_6mths in Mart Extn. If any relevant value='Y', STOP: the collateral has a long-stale price flag and is not reliable for normal recognition. Otherwise continue.",
     "16": "Check haircut_eligible_status in Mart Extn. If any relevant value is not 'Eligible', STOP: the collateral fails the bank's haircut/eligibility rule and is unusable or receives no normal collateral benefit. Otherwise continue.",
-    "17": "Check swwr_flag in Mart Extn. SWWR means Specific Wrong-Way Risk: exposure can increase when the counterparty's credit quality deteriorates. If swwr_flag='Y', inspect swwr_recovery_rate and STOP if a valid rate is present: explain that recognized collateral is reduced using the SWWR recovery treatment and quantify the affected Mart amount. If SWWR is 'N', continue. If SWWR is 'Y' but the recovery rate is missing, continue to Step 18.",
-    "18": "If swwr_flag='Y' but swwr_recovery_rate is blank, zero, negative, or greater than 1, STOP: the SWWR parameter is missing/invalid and the collateral result cannot be trusted. If no such issue exists, continue.",
-    "19": "Reconcile om_cdm_rwa_mtrc.OBLG_ID to om_cdm_rwa_mtrc_extn.principal_gfcid. If a GFC ID in Mart has no matching Mart Extn row for a used balance type, STOP: extension/eligibility data is missing. Otherwise continue.",
-    "20": "Reconcile Mart BAL_TYP_CD to Mart Extn bal_typ_cd. If a balance type used by Mart has no matching Extn record for the same GFC ID, STOP: the balance-type eligibility mapping is incomplete. Otherwise continue.",
-    "21": "For each src_txn_id appearing on more than one collateral balance row, check that NETG_AGR_ID is consistent. If the same source transaction maps to more than one NETG_AGR_ID, STOP: the transaction is split across netting agreements and the collateral benefit may be fragmented. Otherwise continue.",
-    "22": "Across all inbound collateral rows for the GFC ID, identify distinct NETG_AGR_ID values. If multiple agreements exist, verify that they correspond to distinct src_txn_id populations. If the same transaction population is unexpectedly fragmented, STOP and report the agreement IDs and amounts; otherwise continue.",
-    "23": "For rows sharing the same NETG_AGR_ID, check LGL_CERTAINTY_FLG is consistent. If the same agreement has both 'Y' and non-'Y' statuses, STOP: legal-certainty status is inconsistent at agreement level. Otherwise continue.",
-    "24": "Perform a final collateral reconciliation: total FDL_FX_AMT by BAL_TYP_CD, SCR_ID, src_txn_id and NETG_AGR_ID and identify any rows excluded by the checks above. If an exclusion exists, explain the root cause and quantify the potentially impacted collateral amount; otherwise continue.",
-    "25": "If all standard checks pass and no root cause was found, STOP with an inconclusive result: the Mart and Mart Extn contain no evidence explaining the collateral drop. State the checks performed and request human review/upstream history because these tables are current-state snapshots. If the operations user then supplies a one-off additional check using fields already available in Mart/Mart Extn (for example, requiring both BAL_TYP_CD 15 and 16 for a specific source transaction), execute that check as an AD HOC FOLLOW-UP, clearly distinguish it from the standard decision tree, and report whether it resolves the case."
+    "17": "Check swwr_flag in Mart Extn for every relevant bal_typ_cd. SWWR means Specific Wrong-Way Risk: exposure can become worse as the counterparty's credit quality deteriorates. If swwr_flag='Y', inspect swwr_recovery_rate. If the recovery rate is blank, &lt;=0, or &gt;1, STOP: the SWWR parameter is invalid. If a valid rate is present, STOP: SWWR treatment is reducing recognized collateral; quantify the affected Mart FDL_FX_AMT and explain the recovery treatment. If the operations user explicitly says to assume SWWR is not an issue / assume SWWR='N', do not modify source data: record a HYPOTHETICAL case-scoped override for SWWR and continue to Step 18.",
+    "18": "For each scoped src_txn_id, count distinct NETG_AGR_ID values across its collateral rows. If one source transaction maps to more than one netting agreement, STOP: the transaction-to-netting-agreement mapping is fragmented and may split collateral/netting benefit. Report the agreement IDs and affected FDL_FX_AMT. For Case 1 in this demo, src_txn_id 202505198123456SN5 maps to NETG_AGR_ID 2123783 and 2123999. If the operations user explicitly says to assume this mapping is valid / not an issue, do not alter source data: record a second HYPOTHETICAL override for this case and continue to Step 19. Any later reconciliation step must honor this accepted override and must not raise the same mapping issue again.",
+    "19": "Reconcile om_cdm_rwa_mtrc.OBLG_ID to om_cdm_rwa_mtrc_extn.principal_gfcid for the scoped balance types. If a used Mart balance type has no matching Mart Extn row for the GFC ID, STOP: extension/eligibility data is missing. Otherwise continue.",
+    "20": "Reconcile Mart BAL_TYP_CD to Mart Extn bal_typ_cd for the scoped rows. If any scoped balance type has no matching Extn record, STOP: the balance-type eligibility mapping is incomplete. Otherwise continue.",
+    "21": "Review distinct NETG_AGR_ID values across the scoped collateral rows. If a transaction-level multiple-agreement condition was already explicitly accepted by a HYPOTHETICAL override at Step 18, treat that exact condition as accepted for the remainder of this case and do not stop on it again. Otherwise, if unexpected agreement fragmentation remains, STOP and report the affected agreements/amounts. If no unaccepted fragmentation remains, continue.",
+    "22": "For rows sharing the same NETG_AGR_ID, check LGL_CERTAINTY_FLG is consistent. If the same agreement has both 'Y' and non-'Y' statuses, STOP: legal-certainty status is inconsistent at agreement level. Otherwise continue.",
+    "23": "Perform a final collateral reconciliation for the scoped case: total FDL_FX_AMT by BAL_TYP_CD, SCR_ID, src_txn_id and NETG_AGR_ID. Exclude only conditions that the human explicitly accepted as HYPOTHETICAL overrides. If any new, non-overridden exclusion or inconsistency is found, STOP and explain it; otherwise continue.",
+    "24": "Confirm that all remaining standard checks passed after applying any case-scoped HYPOTHETICAL overrides. Do not reinterpret an overridden condition as factual source data; preserve the actual values in the explanation. If all remaining checks pass, continue.",
+    "25": "STOP at end of tree with 'no further issue found under the stated assumptions' if every remaining check passes. State the actual source-data blockers that were bypassed (for example SWWR='Y' and/or multiple NETG_AGR_ID values), state each human-supplied hypothetical assumption separately, and conclude that the current Mart/Mart Extn data contains no additional failure beyond those assumed-away conditions. Do not claim the source data itself is clean."
 }</x:v>
       </x:c>
     </x:row>
